--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N112_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N112_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.40991226214056</v>
+        <v>6.891610742597841</v>
       </c>
       <c r="D2" t="n">
-        <v>42.47719054356038</v>
+        <v>6.902543463328563</v>
       </c>
       <c r="E2" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F2" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58506959317376</v>
+        <v>3.670073808890737</v>
       </c>
       <c r="D3" t="n">
-        <v>22.78776275930201</v>
+        <v>3.703011448386577</v>
       </c>
       <c r="E3" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F3" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.26358564033328</v>
+        <v>6.217832666554159</v>
       </c>
       <c r="D4" t="n">
-        <v>38.13671998460899</v>
+        <v>6.197216997498962</v>
       </c>
       <c r="E4" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F4" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.98248554865879</v>
+        <v>5.359653901657055</v>
       </c>
       <c r="D5" t="n">
-        <v>32.73397150784201</v>
+        <v>5.319270370024326</v>
       </c>
       <c r="E5" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F5" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.49637417949645</v>
+        <v>9.018160804168174</v>
       </c>
       <c r="D6" t="n">
-        <v>55.24297820915233</v>
+        <v>8.976983958987255</v>
       </c>
       <c r="E6" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F6" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.80080327750256</v>
+        <v>4.680130532594167</v>
       </c>
       <c r="D7" t="n">
-        <v>28.53011328944291</v>
+        <v>4.636143409534473</v>
       </c>
       <c r="E7" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F7" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.217496314465614</v>
+        <v>1.010343151100662</v>
       </c>
       <c r="D8" t="n">
-        <v>5.935396800729146</v>
+        <v>0.9645019801184862</v>
       </c>
       <c r="E8" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F8" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.3398107777096</v>
+        <v>6.55521925137781</v>
       </c>
       <c r="D9" t="n">
-        <v>40.06060245218356</v>
+        <v>6.509847898479829</v>
       </c>
       <c r="E9" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F9" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.23928214061239</v>
+        <v>4.263883347849514</v>
       </c>
       <c r="D10" t="n">
-        <v>26.3416933202189</v>
+        <v>4.280525164535572</v>
       </c>
       <c r="E10" t="n">
-        <v>13.18177607606366</v>
+        <v>2.142038612360345</v>
       </c>
       <c r="F10" t="n">
-        <v>13.16333605980099</v>
+        <v>2.13904210971766</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
